--- a/output/2026-09-03_23_Italia_Basilicata_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-03_23_Italia_Basilicata_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ingrosso/dettaglio ferramenta, colori, utensileria. P.IVA 00913820767, Lavello (PZ), attiva dal 1952.</t>
+          <t>Ingrosso/dettaglio ferramenta, colori, utensileria. P.IVA 00913820767, Lavello (PZ), attiva dal 1952. [DUPLICATO — vedi anche: 2026-09-03_20_Italia_Basilicata_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">

--- a/output/2026-09-03_23_Italia_Basilicata_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-03_23_Italia_Basilicata_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vendita e noleggio gruppi elettrogeni, compressori, saldatrici, torri faro, attrezzature per cantieri/industria. Fondata 1990, Viggiano (PZ).</t>
+          <t>Vendita e noleggio gruppi elettrogeni, compressori, saldatrici, torri faro, attrezzature per cantieri/industria. Fondata 1990, Viggiano (PZ). [DUPLICATO — vedi anche: 2026-09-03_19_Italia_Basilicata_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
